--- a/artfynd/A 53650-2025 artfynd.xlsx
+++ b/artfynd/A 53650-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>129000334</v>
       </c>
       <c r="B3" t="n">
-        <v>80182</v>
+        <v>80184</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53650-2025 artfynd.xlsx
+++ b/artfynd/A 53650-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>129000334</v>
       </c>
       <c r="B3" t="n">
-        <v>80184</v>
+        <v>80185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 53650-2025 artfynd.xlsx
+++ b/artfynd/A 53650-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103957161</v>
+        <v>129000334</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,24 +708,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stenkulla, Ly lm</t>
+          <t>Rusfors, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>657962.9483214027</v>
+        <v>657599</v>
       </c>
       <c r="R2" t="n">
-        <v>7182004.622393992</v>
+        <v>7182221</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,22 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-10-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,44 +769,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129000334</v>
+        <v>103957161</v>
       </c>
       <c r="B3" t="n">
-        <v>80185</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -832,16 +814,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rusfors, Ly lm</t>
+          <t>Stenkulla, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>657599</v>
+        <v>657963</v>
       </c>
       <c r="R3" t="n">
-        <v>7182221</v>
+        <v>7182004</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,17 +858,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2022-10-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,12 +878,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 53650-2025 artfynd.xlsx
+++ b/artfynd/A 53650-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000334</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,8 +897,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103957161</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>